--- a/data/trans_dic/IP41-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,79; 97,6</t>
+          <t>90,84; 97,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,35; 96,43</t>
+          <t>90,39; 96,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,9; 92,44</t>
+          <t>83,41; 92,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,19; 95,11</t>
+          <t>86,62; 95,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,36; 94,52</t>
+          <t>86,65; 94,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,28; 91,99</t>
+          <t>83,14; 92,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90,26; 95,62</t>
+          <t>90,13; 95,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89,96; 94,82</t>
+          <t>89,89; 94,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84,9; 91,27</t>
+          <t>84,6; 91,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,67; 93,48</t>
+          <t>87,63; 93,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,9; 90,84</t>
+          <t>83,52; 90,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,41; 90,0</t>
+          <t>82,25; 89,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,15; 95,3</t>
+          <t>90,4; 95,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,75; 92,54</t>
+          <t>85,88; 92,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,08; 86,93</t>
+          <t>79,14; 86,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,75; 93,71</t>
+          <t>89,78; 93,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86,13; 90,85</t>
+          <t>86,1; 90,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,76; 87,15</t>
+          <t>81,77; 87,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,0; 90,46</t>
+          <t>79,49; 89,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,44; 91,87</t>
+          <t>83,57; 92,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,69; 84,06</t>
+          <t>74,27; 83,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,67; 95,34</t>
+          <t>87,92; 95,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,85; 92,27</t>
+          <t>83,51; 92,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,09; 85,71</t>
+          <t>76,55; 86,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,38; 92,04</t>
+          <t>85,55; 91,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,23; 91,32</t>
+          <t>85,2; 91,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,88; 83,5</t>
+          <t>76,94; 83,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,72; 95,75</t>
+          <t>89,96; 95,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,05; 91,33</t>
+          <t>83,38; 91,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,22; 87,3</t>
+          <t>77,72; 87,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,73; 94,76</t>
+          <t>88,86; 94,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,9; 87,92</t>
+          <t>79,27; 87,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,95; 87,96</t>
+          <t>78,83; 88,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,3; 94,61</t>
+          <t>90,09; 94,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82,71; 88,71</t>
+          <t>82,34; 88,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,38; 86,65</t>
+          <t>79,47; 86,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,21; 92,68</t>
+          <t>89,09; 92,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,23; 91,04</t>
+          <t>87,17; 90,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,72; 86,33</t>
+          <t>81,58; 86,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,57; 93,92</t>
+          <t>90,68; 93,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,16; 90,13</t>
+          <t>86,18; 90,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,43; 85,92</t>
+          <t>81,4; 85,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,95</t>
+          <t>90,53; 92,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,33; 89,99</t>
+          <t>87,36; 90,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,22; 85,45</t>
+          <t>82,43; 85,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>98868</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>138020</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>116768</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>110066</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>133186</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>109378</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>208934</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>271206</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>226146</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>94561; 101670</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>132650; 142056</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>109817; 121674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>103885; 114252</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>126498; 137756</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>103228; 115152</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>201913; 214248</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>263163; 277266</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>216420; 233283</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>227081</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>207385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>182346</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>234770</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>240365</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>214364</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>461852</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>447749</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>396711</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>219340; 233706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>197310; 214599</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>173144; 189353</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>228242; 240871</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>231016; 247648</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>203716; 223842</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>451425; 470964</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>435020; 457456</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>382644; 407965</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>107166</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137740</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149291</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>128189</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>140751</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>153389</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>235355</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>278491</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>302680</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>99810; 112615</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>130642; 144101</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139623; 157523</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>122149; 132283</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>132428; 146080</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>143855; 161893</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>226271; 242465</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>268278; 287371</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>289236; 314125</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>178358</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150578</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143871</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>188112</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>150930</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>145639</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>366470</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>301508</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>289509</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>172084; 183481</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>142854; 156777</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>134697; 152082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>181531; 193949</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>142650; 157968</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>137202; 153292</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>356356; 374322</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>289245; 311205</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>276032; 299995</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>611473</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>633723</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>592276</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1272611</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1298955</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1215045</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>598015; 623118</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>619496; 646671</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>573893; 606252</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>648912; 671860</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>649341; 679132</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>605264; 638164</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1255626; 1288520</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1279167; 1318438</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1192798; 1236343</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP41-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -519,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -632,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>88,4%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,84; 97,67</t>
+          <t>90,92; 97,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,39; 96,79</t>
+          <t>90,37; 96,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,41; 92,42</t>
+          <t>83,67; 92,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,79; 95,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,62; 95,27</t>
+          <t>86,67; 94,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,65; 94,36</t>
+          <t>82,92; 92,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,14; 92,74</t>
+          <t>89,56; 95,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,16; 94,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90,13; 95,64</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>89,89; 94,71</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84,6; 91,19</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>85,02; 91,41</t>
         </is>
       </c>
     </row>
@@ -804,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>84,78%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,63; 93,37</t>
+          <t>87,28; 93,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,52; 90,84</t>
+          <t>83,62; 90,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,25; 89,95</t>
+          <t>82,56; 90,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,01; 95,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,4; 95,4</t>
+          <t>85,71; 91,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,88; 92,07</t>
+          <t>78,97; 86,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,14; 86,95</t>
+          <t>89,59; 93,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,2; 90,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,78; 93,67</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86,1; 90,54</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81,77; 87,18</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>81,95; 87,21</t>
         </is>
       </c>
     </row>
@@ -944,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>80,52%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,49; 89,68</t>
+          <t>79,54; 89,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,57; 92,18</t>
+          <t>83,33; 91,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,27; 83,79</t>
+          <t>74,39; 84,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,86; 95,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,92; 95,21</t>
+          <t>83,49; 92,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,51; 92,12</t>
+          <t>76,53; 85,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,55; 86,15</t>
+          <t>85,22; 91,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,89; 90,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,55; 91,67</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85,2; 91,26</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>76,94; 83,56</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>77,06; 83,49</t>
         </is>
       </c>
     </row>
@@ -1084,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>85,83%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>83,35%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,96; 95,92</t>
+          <t>90,09; 96,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,38; 91,5</t>
+          <t>83,59; 91,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,72; 87,76</t>
+          <t>77,84; 87,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,98; 94,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,86; 94,94</t>
+          <t>78,98; 88,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,27; 87,78</t>
+          <t>78,67; 87,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,83; 88,07</t>
+          <t>90,06; 94,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,52; 88,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,63</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>82,34; 88,59</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79,47; 86,37</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>79,51; 86,55</t>
         </is>
       </c>
     </row>
@@ -1224,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>88,72%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>83,97%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,09; 92,83</t>
+          <t>89,0; 92,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,17; 90,99</t>
+          <t>87,29; 91,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,58; 86,18</t>
+          <t>81,96; 86,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,69; 93,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,68; 93,88</t>
+          <t>86,2; 90,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,18; 90,13</t>
+          <t>81,32; 85,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,4; 85,83</t>
+          <t>90,55; 92,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,25; 90,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,91</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>87,36; 90,05</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>82,43; 85,44</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>82,42; 85,46</t>
         </is>
       </c>
     </row>
@@ -1345,15 +1171,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1365,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1379,15 +1205,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1398,23 +1221,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1436,47 +1256,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1492,9 +1297,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1524,47 +1326,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>352</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1592,47 +1379,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>110066</t>
+          <t>133186</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>133186</t>
+          <t>109378</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>109378</t>
+          <t>208934</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271206</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>208934</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>271206</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
           <t>226146</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94561; 101670</t>
+          <t>94648; 101519</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132650; 142056</t>
+          <t>132626; 142007</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109817; 121674</t>
+          <t>110155; 121738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>104090; 114220</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>103885; 114252</t>
+          <t>126535; 137908</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>126498; 137756</t>
+          <t>102962; 114753</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>103228; 115152</t>
+          <t>200643; 214023</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>263932; 277838</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>201913; 214248</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>263163; 277266</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>216420; 233283</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>217502; 233831</t>
         </is>
       </c>
     </row>
@@ -1732,47 +1489,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>316</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>694</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>632</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
           <t>604</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1800,47 +1542,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234770</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>234770</t>
+          <t>240365</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>240365</t>
+          <t>214364</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>214364</t>
+          <t>461852</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447749</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>461852</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>447749</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>396711</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>219340; 233706</t>
+          <t>218466; 233511</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>197310; 214599</t>
+          <t>197558; 214366</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173144; 189353</t>
+          <t>173810; 189462</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>227271; 240516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>228242; 240871</t>
+          <t>230559; 247045</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>231016; 247648</t>
+          <t>203296; 223636</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>203716; 223842</t>
+          <t>450451; 470852</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>435531; 458615</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>451425; 470964</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>435020; 457456</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>382644; 407965</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>383474; 408103</t>
         </is>
       </c>
     </row>
@@ -1940,47 +1652,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>214</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>431</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2008,47 +1705,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>128189</t>
+          <t>140751</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>140751</t>
+          <t>153389</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>153389</t>
+          <t>235355</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>278491</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>235355</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>278491</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
           <t>302680</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2061,62 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99810; 112615</t>
+          <t>99883; 112792</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130642; 144101</t>
+          <t>130265; 143551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139623; 157523</t>
+          <t>139855; 158056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>122067; 132331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>122149; 132283</t>
+          <t>132386; 146347</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>132428; 146080</t>
+          <t>143820; 161306</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>143855; 161893</t>
+          <t>225415; 242698</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>267300; 286378</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>226271; 242465</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>268278; 287371</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>289236; 314125</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>289672; 313851</t>
         </is>
       </c>
     </row>
@@ -2148,47 +1815,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>546</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>435</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
           <t>402</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2216,47 +1868,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>188112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>188112</t>
+          <t>150930</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>150930</t>
+          <t>145639</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>145639</t>
+          <t>366470</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>301508</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>366470</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>301508</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>289509</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2269,62 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172084; 183481</t>
+          <t>172320; 183672</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>142854; 156777</t>
+          <t>143226; 156901</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134697; 152082</t>
+          <t>134890; 152273</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>181783; 193525</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>181531; 193949</t>
+          <t>142128; 158488</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>142650; 157968</t>
+          <t>136925; 152866</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>137202; 153292</t>
+          <t>356233; 373858</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>289903; 311106</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>356356; 374322</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>289245; 311205</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>276032; 299995</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>276166; 300633</t>
         </is>
       </c>
     </row>
@@ -2356,47 +1978,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>947</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>893</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>1789</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2424,47 +2031,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>661138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>661138</t>
+          <t>665232</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>665232</t>
+          <t>622770</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>622770</t>
+          <t>1272611</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1298955</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1272611</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1298955</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
           <t>1215045</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>598015; 623118</t>
+          <t>597408; 622663</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>619496; 646671</t>
+          <t>620351; 647122</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>573893; 606252</t>
+          <t>576591; 607939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>648998; 671824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>648912; 671860</t>
+          <t>649515; 678391</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>649341; 679132</t>
+          <t>604626; 638256</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>605264; 638164</t>
+          <t>1255897; 1287529</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1277477; 1317922</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1255626; 1288520</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1279167; 1318438</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1192798; 1236343</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1192569; 1236573</t>
         </is>
       </c>
     </row>
@@ -2545,14 +2122,14 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/IP41-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>94,97%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>88,69%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,92; 97,52</t>
+          <t>87,19; 95,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,37; 96,76</t>
+          <t>86,36; 94,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,67; 92,47</t>
+          <t>82,28; 91,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,79; 95,24</t>
+          <t>90,79; 97,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,67; 94,46</t>
+          <t>90,35; 96,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,92; 92,42</t>
+          <t>83,9; 92,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,56; 95,53</t>
+          <t>90,26; 95,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,16; 94,91</t>
+          <t>89,96; 94,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,02; 91,41</t>
+          <t>84,9; 91,27</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83,27%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>90,72%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>87,78%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>86,62%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>89,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>83,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,28; 93,29</t>
+          <t>90,15; 95,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,62; 90,74</t>
+          <t>85,75; 92,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,56; 90,0</t>
+          <t>79,08; 86,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,01; 95,26</t>
+          <t>87,67; 93,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,71; 91,84</t>
+          <t>83,9; 90,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,97; 86,87</t>
+          <t>82,41; 90,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,59; 93,64</t>
+          <t>89,75; 93,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,2; 90,77</t>
+          <t>86,13; 90,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,95; 87,21</t>
+          <t>81,76; 87,15</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>92,27%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>85,34%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>88,11%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>79,41%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,54; 89,82</t>
+          <t>87,67; 95,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,33; 91,83</t>
+          <t>83,85; 92,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,39; 84,07</t>
+          <t>76,09; 85,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,86; 95,25</t>
+          <t>80,0; 90,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,49; 92,29</t>
+          <t>83,44; 91,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,53; 85,84</t>
+          <t>73,69; 84,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,22; 91,76</t>
+          <t>85,38; 92,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,89; 90,94</t>
+          <t>85,23; 91,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,06; 83,49</t>
+          <t>76,88; 83,5</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83,87%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>93,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>87,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>83,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>83,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,09; 96,02</t>
+          <t>88,73; 94,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,59; 91,57</t>
+          <t>78,9; 87,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,84; 87,87</t>
+          <t>77,95; 87,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,98; 94,73</t>
+          <t>89,72; 95,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,98; 88,07</t>
+          <t>83,05; 91,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,67; 87,83</t>
+          <t>78,22; 87,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,06; 94,51</t>
+          <t>90,3; 94,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,52; 88,56</t>
+          <t>82,71; 88,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,51; 86,55</t>
+          <t>79,38; 86,65</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>88,28%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>89,17%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,0; 92,76</t>
+          <t>90,57; 93,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,29; 91,06</t>
+          <t>86,16; 90,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,96; 86,42</t>
+          <t>81,43; 85,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,69; 93,88</t>
+          <t>89,21; 92,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,2; 90,03</t>
+          <t>87,23; 91,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,32; 85,84</t>
+          <t>81,72; 86,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,83</t>
+          <t>90,55; 92,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,25; 90,01</t>
+          <t>87,33; 89,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82,42; 85,46</t>
+          <t>82,22; 85,45</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>187</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>110066</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>133186</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>109378</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>98868</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>138020</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>116768</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>110066</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>133186</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>109378</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94648; 101519</t>
+          <t>104567; 114062</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132626; 142007</t>
+          <t>126077; 137994</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110155; 121738</t>
+          <t>102158; 114218</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104090; 114220</t>
+          <t>94515; 101604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>126535; 137908</t>
+          <t>132594; 141520</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>102962; 114753</t>
+          <t>110452; 121706</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>200643; 214023</t>
+          <t>202197; 214213</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>263932; 277838</t>
+          <t>263359; 277585</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217502; 233831</t>
+          <t>217181; 233478</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>298</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>288</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>234770</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>240365</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>214364</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>227081</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>207385</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>182346</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>234770</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>240365</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>214364</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>218466; 233511</t>
+          <t>227632; 240618</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>197558; 214366</t>
+          <t>230658; 248915</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173810; 189462</t>
+          <t>203582; 223783</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>227271; 240516</t>
+          <t>219457; 234005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>230559; 247045</t>
+          <t>198212; 214608</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>203296; 223636</t>
+          <t>173497; 189462</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>450451; 470852</t>
+          <t>451293; 471156</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>435531; 458615</t>
+          <t>435183; 459036</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>383474; 408103</t>
+          <t>382599; 407809</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>195</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>217</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>128189</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140751</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153389</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>107166</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>137740</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>149291</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>128189</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>140751</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>153389</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99883; 112792</t>
+          <t>121806; 132458</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130265; 143551</t>
+          <t>132955; 146312</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139855; 158056</t>
+          <t>142981; 161072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122067; 132331</t>
+          <t>100462; 113592</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>132386; 146347</t>
+          <t>130434; 143612</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>143820; 161306</t>
+          <t>138543; 158023</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>225415; 242698</t>
+          <t>225841; 243450</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>267300; 286378</t>
+          <t>268395; 287549</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>289672; 313851</t>
+          <t>288990; 313884</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>204</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>188112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150930</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>145639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>178358</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>150578</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>143871</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>188112</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>150930</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>145639</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172320; 183672</t>
+          <t>181270; 193575</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>143226; 156901</t>
+          <t>141979; 158223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134890; 152273</t>
+          <t>135671; 153098</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>181783; 193525</t>
+          <t>171608; 183156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142128; 158488</t>
+          <t>142298; 156483</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>136925; 152866</t>
+          <t>135562; 151297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>356233; 373858</t>
+          <t>357187; 374243</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>289903; 311106</t>
+          <t>290539; 311615</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>276166; 300633</t>
+          <t>275714; 300971</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>912</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>896</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>611473</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>633723</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>592276</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>661138</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665232</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>622770</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>597408; 622663</t>
+          <t>648186; 672164</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>620351; 647122</t>
+          <t>649247; 679152</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>576591; 607939</t>
+          <t>605446; 638865</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>648998; 671824</t>
+          <t>598853; 622097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>649515; 678391</t>
+          <t>619897; 647022</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>604626; 638256</t>
+          <t>574859; 607310</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1255897; 1287529</t>
+          <t>1255890; 1289194</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1277477; 1317922</t>
+          <t>1278637; 1317666</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1192569; 1236573</t>
+          <t>1189699; 1236418</t>
         </is>
       </c>
     </row>
